--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\AO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\AO\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Maqaa</t>
   </si>
@@ -38,16 +38,34 @@
     <t>Waliigal.Fudhatu</t>
   </si>
   <si>
-    <t>Lammii Diroo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fayyisaa Badhuu </t>
   </si>
   <si>
-    <t>Girmaa Qorichoo</t>
-  </si>
-  <si>
     <t>Hannaa Addunyaa</t>
+  </si>
+  <si>
+    <t>Barsiisaa Margaa</t>
+  </si>
+  <si>
+    <t>Girmaa Masqalaa</t>
+  </si>
+  <si>
+    <t>Mangee Lammaa</t>
+  </si>
+  <si>
+    <t>Lalisee Magarsaa</t>
+  </si>
+  <si>
+    <t>Jabeessaa Margaa</t>
+  </si>
+  <si>
+    <t>Walfaanaa Magarsaa</t>
+  </si>
+  <si>
+    <t>Baqqalaa barsiisaa</t>
+  </si>
+  <si>
+    <t>Salamoon Zarihuun</t>
   </si>
 </sst>
 </file>
@@ -369,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -393,10 +411,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1">
-        <v>922956646</v>
+        <v>930308503</v>
       </c>
       <c r="C2">
         <v>5000</v>
@@ -407,7 +425,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>977677737</v>
@@ -421,10 +439,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>910814723</v>
+        <v>913354650</v>
       </c>
       <c r="C4">
         <v>5000</v>
@@ -435,7 +453,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>917372534</v>
@@ -444,6 +462,87 @@
         <v>5000</v>
       </c>
       <c r="D5">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>919408998</v>
+      </c>
+      <c r="C6">
+        <v>5000</v>
+      </c>
+      <c r="D6">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>954846351</v>
+      </c>
+      <c r="C7">
+        <v>5000</v>
+      </c>
+      <c r="D7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>912695064</v>
+      </c>
+      <c r="C8">
+        <v>5000</v>
+      </c>
+      <c r="D8">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>912861188</v>
+      </c>
+      <c r="C9">
+        <v>5000</v>
+      </c>
+      <c r="D9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>5000</v>
+      </c>
+      <c r="D10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1">
+        <v>926757080</v>
+      </c>
+      <c r="C11">
+        <v>5000</v>
+      </c>
+      <c r="D11">
         <v>30000</v>
       </c>
     </row>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Maqaa</t>
   </si>
@@ -62,10 +62,28 @@
     <t>Walfaanaa Magarsaa</t>
   </si>
   <si>
-    <t>Baqqalaa barsiisaa</t>
-  </si>
-  <si>
     <t>Salamoon Zarihuun</t>
+  </si>
+  <si>
+    <t>Baqqalaa Tolasaa</t>
+  </si>
+  <si>
+    <t>Lammii Diroo</t>
+  </si>
+  <si>
+    <t>Qananiisaa Biqilaa</t>
+  </si>
+  <si>
+    <t>Dajanee Guutaa</t>
+  </si>
+  <si>
+    <t>Warqii Lammaa</t>
+  </si>
+  <si>
+    <t>Baqqalaa Barsiisaa</t>
+  </si>
+  <si>
+    <t>Getuu Baqqalaa</t>
   </si>
 </sst>
 </file>
@@ -387,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -420,7 +438,7 @@
         <v>5000</v>
       </c>
       <c r="D2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -434,7 +452,7 @@
         <v>5000</v>
       </c>
       <c r="D3">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -448,7 +466,7 @@
         <v>5000</v>
       </c>
       <c r="D4">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -462,7 +480,7 @@
         <v>5000</v>
       </c>
       <c r="D5">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -476,7 +494,7 @@
         <v>5000</v>
       </c>
       <c r="D6">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -490,7 +508,7 @@
         <v>5000</v>
       </c>
       <c r="D7">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -504,7 +522,7 @@
         <v>5000</v>
       </c>
       <c r="D8">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -518,23 +536,26 @@
         <v>5000</v>
       </c>
       <c r="D9">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>912218826</v>
       </c>
       <c r="C10">
         <v>5000</v>
       </c>
       <c r="D10">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
         <v>926757080</v>
@@ -543,7 +564,91 @@
         <v>5000</v>
       </c>
       <c r="D11">
-        <v>30000</v>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>928276274</v>
+      </c>
+      <c r="C12">
+        <v>5000</v>
+      </c>
+      <c r="D12">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9229556646</v>
+      </c>
+      <c r="C13">
+        <v>5000</v>
+      </c>
+      <c r="D13">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>911818685</v>
+      </c>
+      <c r="C14">
+        <v>5000</v>
+      </c>
+      <c r="D14">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>913216895</v>
+      </c>
+      <c r="C15">
+        <v>5000</v>
+      </c>
+      <c r="D15">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>947763811</v>
+      </c>
+      <c r="C16">
+        <v>5000</v>
+      </c>
+      <c r="D16">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1">
+        <v>912672957</v>
+      </c>
+      <c r="C17">
+        <v>5000</v>
+      </c>
+      <c r="D17">
+        <v>40000</v>
       </c>
     </row>
   </sheetData>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Maqaa</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Getuu Baqqalaa</t>
+  </si>
+  <si>
+    <t>Silashii Dhabasaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biraanuu </t>
   </si>
 </sst>
 </file>
@@ -405,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -438,7 +444,7 @@
         <v>5000</v>
       </c>
       <c r="D2">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -452,7 +458,7 @@
         <v>5000</v>
       </c>
       <c r="D3">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -466,7 +472,7 @@
         <v>5000</v>
       </c>
       <c r="D4">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -477,10 +483,10 @@
         <v>917372534</v>
       </c>
       <c r="C5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D5">
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -494,7 +500,7 @@
         <v>5000</v>
       </c>
       <c r="D6">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -508,7 +514,7 @@
         <v>5000</v>
       </c>
       <c r="D7">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -522,7 +528,7 @@
         <v>5000</v>
       </c>
       <c r="D8">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -536,7 +542,7 @@
         <v>5000</v>
       </c>
       <c r="D9">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -550,7 +556,7 @@
         <v>5000</v>
       </c>
       <c r="D10">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -564,7 +570,7 @@
         <v>5000</v>
       </c>
       <c r="D11">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -578,7 +584,7 @@
         <v>5000</v>
       </c>
       <c r="D12">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -592,7 +598,7 @@
         <v>5000</v>
       </c>
       <c r="D13">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -606,7 +612,7 @@
         <v>5000</v>
       </c>
       <c r="D14">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -620,7 +626,7 @@
         <v>5000</v>
       </c>
       <c r="D15">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -634,7 +640,7 @@
         <v>5000</v>
       </c>
       <c r="D16">
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -648,7 +654,35 @@
         <v>5000</v>
       </c>
       <c r="D17">
-        <v>40000</v>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="1">
+        <v>985816078</v>
+      </c>
+      <c r="C18">
+        <v>5000</v>
+      </c>
+      <c r="D18">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1">
+        <v>924897677</v>
+      </c>
+      <c r="C19">
+        <v>10000</v>
+      </c>
+      <c r="D19">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -41,9 +41,6 @@
     <t xml:space="preserve">Fayyisaa Badhuu </t>
   </si>
   <si>
-    <t>Hannaa Addunyaa</t>
-  </si>
-  <si>
     <t>Barsiisaa Margaa</t>
   </si>
   <si>
@@ -90,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">Biraanuu </t>
+  </si>
+  <si>
+    <t>Abarraa Asaffaa</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>930308503</v>
@@ -463,7 +463,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>913354650</v>
@@ -477,7 +477,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>917372534</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>919408998</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>954846351</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>912695064</v>
@@ -533,7 +533,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>912861188</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
         <v>912218826</v>
@@ -561,21 +561,21 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1">
         <v>926757080</v>
       </c>
       <c r="C11">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D11">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1">
         <v>928276274</v>
@@ -589,7 +589,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1">
         <v>9229556646</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
         <v>911818685</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1">
         <v>913216895</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1">
         <v>947763811</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1">
         <v>912672957</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1">
         <v>985816078</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="1">
         <v>924897677</v>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Maqaa</t>
   </si>
@@ -50,21 +50,12 @@
     <t>Mangee Lammaa</t>
   </si>
   <si>
-    <t>Lalisee Magarsaa</t>
-  </si>
-  <si>
-    <t>Jabeessaa Margaa</t>
-  </si>
-  <si>
     <t>Walfaanaa Magarsaa</t>
   </si>
   <si>
     <t>Salamoon Zarihuun</t>
   </si>
   <si>
-    <t>Baqqalaa Tolasaa</t>
-  </si>
-  <si>
     <t>Lammii Diroo</t>
   </si>
   <si>
@@ -86,10 +77,10 @@
     <t>Silashii Dhabasaa</t>
   </si>
   <si>
-    <t xml:space="preserve">Biraanuu </t>
-  </si>
-  <si>
     <t>Abarraa Asaffaa</t>
+  </si>
+  <si>
+    <t>Jabeessaa Caalaa</t>
   </si>
 </sst>
 </file>
@@ -411,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -455,10 +446,10 @@
         <v>977677737</v>
       </c>
       <c r="C3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D3">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -477,7 +468,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>917372534</v>
@@ -505,10 +496,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1">
-        <v>954846351</v>
+        <v>912695064</v>
       </c>
       <c r="C7">
         <v>5000</v>
@@ -519,10 +510,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>912695064</v>
+        <v>912861188</v>
       </c>
       <c r="C8">
         <v>5000</v>
@@ -533,10 +524,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>912861188</v>
+        <v>912218826</v>
       </c>
       <c r="C9">
         <v>5000</v>
@@ -547,66 +538,66 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>912218826</v>
+        <v>926757080</v>
       </c>
       <c r="C10">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D10">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>926757080</v>
+        <v>9229556646</v>
       </c>
       <c r="C11">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="D11">
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>928276274</v>
+        <v>911818685</v>
       </c>
       <c r="C12">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D12">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>9229556646</v>
+        <v>913216895</v>
       </c>
       <c r="C13">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D13">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>911818685</v>
+        <v>947763811</v>
       </c>
       <c r="C14">
         <v>5000</v>
@@ -620,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>913216895</v>
+        <v>912672957</v>
       </c>
       <c r="C15">
         <v>5000</v>
@@ -634,55 +625,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>947763811</v>
+        <v>985816078</v>
       </c>
       <c r="C16">
         <v>5000</v>
       </c>
       <c r="D16">
         <v>50000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1">
-        <v>912672957</v>
-      </c>
-      <c r="C17">
-        <v>5000</v>
-      </c>
-      <c r="D17">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C18">
-        <v>5000</v>
-      </c>
-      <c r="D18">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>924897677</v>
-      </c>
-      <c r="C19">
-        <v>10000</v>
-      </c>
-      <c r="D19">
-        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Maqaa</t>
   </si>
@@ -41,46 +41,28 @@
     <t xml:space="preserve">Fayyisaa Badhuu </t>
   </si>
   <si>
-    <t>Barsiisaa Margaa</t>
-  </si>
-  <si>
-    <t>Girmaa Masqalaa</t>
-  </si>
-  <si>
-    <t>Mangee Lammaa</t>
-  </si>
-  <si>
-    <t>Walfaanaa Magarsaa</t>
-  </si>
-  <si>
     <t>Salamoon Zarihuun</t>
   </si>
   <si>
-    <t>Lammii Diroo</t>
-  </si>
-  <si>
     <t>Qananiisaa Biqilaa</t>
   </si>
   <si>
     <t>Dajanee Guutaa</t>
   </si>
   <si>
-    <t>Warqii Lammaa</t>
-  </si>
-  <si>
-    <t>Baqqalaa Barsiisaa</t>
-  </si>
-  <si>
-    <t>Getuu Baqqalaa</t>
-  </si>
-  <si>
-    <t>Silashii Dhabasaa</t>
-  </si>
-  <si>
     <t>Abarraa Asaffaa</t>
   </si>
   <si>
-    <t>Jabeessaa Caalaa</t>
+    <t xml:space="preserve">Barsiisaa Margaa fi Baqqalaa Barsiisaa  </t>
+  </si>
+  <si>
+    <t>Girmaa Masqalaa fi Lammii Diroo</t>
+  </si>
+  <si>
+    <t>Jabeessaa Caalaa fi Getuu Baqqalaa</t>
+  </si>
+  <si>
+    <t>Warqii Lammaa fi Silashii Dhabasaa</t>
   </si>
 </sst>
 </file>
@@ -402,10 +384,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -426,16 +408,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>930308503</v>
+        <v>912218826</v>
       </c>
       <c r="C2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -454,21 +436,21 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>913354650</v>
       </c>
       <c r="C4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D4">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>917372534</v>
@@ -482,156 +464,72 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>919408998</v>
+        <v>912695064</v>
       </c>
       <c r="C6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D6">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>912695064</v>
+        <v>926757080</v>
       </c>
       <c r="C7">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D7">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>912861188</v>
+        <v>911818685</v>
       </c>
       <c r="C8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D8">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>912218826</v>
+        <v>913216895</v>
       </c>
       <c r="C9">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D9">
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>926757080</v>
+        <v>985816078</v>
       </c>
       <c r="C10">
         <v>10000</v>
       </c>
       <c r="D10">
         <v>100000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9229556646</v>
-      </c>
-      <c r="C11">
-        <v>5000</v>
-      </c>
-      <c r="D11">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <v>911818685</v>
-      </c>
-      <c r="C12">
-        <v>10000</v>
-      </c>
-      <c r="D12">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <v>913216895</v>
-      </c>
-      <c r="C13">
-        <v>10000</v>
-      </c>
-      <c r="D13">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>947763811</v>
-      </c>
-      <c r="C14">
-        <v>5000</v>
-      </c>
-      <c r="D14">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
-        <v>912672957</v>
-      </c>
-      <c r="C15">
-        <v>5000</v>
-      </c>
-      <c r="D15">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C16">
-        <v>5000</v>
-      </c>
-      <c r="D16">
-        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Maqaa</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Abarraa Asaffaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barsiisaa Margaa fi Baqqalaa Barsiisaa  </t>
   </si>
   <si>
     <t>Girmaa Masqalaa fi Lammii Diroo</t>
@@ -384,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -408,10 +405,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>912218826</v>
+        <v>977677737</v>
       </c>
       <c r="C2">
         <v>10000</v>
@@ -422,10 +419,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>977677737</v>
+        <v>913354650</v>
       </c>
       <c r="C3">
         <v>10000</v>
@@ -436,10 +433,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
-        <v>913354650</v>
+        <v>917372534</v>
       </c>
       <c r="C4">
         <v>10000</v>
@@ -450,10 +447,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>917372534</v>
+        <v>912695064</v>
       </c>
       <c r="C5">
         <v>10000</v>
@@ -464,10 +461,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>912695064</v>
+        <v>926757080</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -478,10 +475,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>926757080</v>
+        <v>911818685</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -492,10 +489,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>911818685</v>
+        <v>913216895</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -506,29 +503,15 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>913216895</v>
+        <v>985816078</v>
       </c>
       <c r="C9">
         <v>10000</v>
       </c>
       <c r="D9">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C10">
-        <v>10000</v>
-      </c>
-      <c r="D10">
         <v>100000</v>
       </c>
     </row>
